--- a/1-LATEX/2-DADOS/3-OUTPUT/mapa_heterogeneidade.xlsx
+++ b/1-LATEX/2-DADOS/3-OUTPUT/mapa_heterogeneidade.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -394,7 +394,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Erosão Intergeracional</t>
+          <t>Erosao Intergeracional</t>
         </is>
       </c>
       <c r="C2">
@@ -426,10 +426,10 @@
         </is>
       </c>
       <c r="C3">
-        <v>2.438881119934042</v>
+        <v>3.642037642435129</v>
       </c>
       <c r="D3">
-        <v>0.02121684598240538</v>
+        <v>0.02389601709455585</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -450,14 +450,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Singularidade Territorial</t>
+          <t>Status de Documentacao</t>
         </is>
       </c>
       <c r="C4">
-        <v>6.074724194413331</v>
+        <v>7.629654219477611</v>
       </c>
       <c r="D4">
-        <v>0.02766083366641499</v>
+        <v>0.09260327465062979</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -478,23 +478,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Status de Documentação</t>
+          <t>Vulnerabilidade Juridica</t>
         </is>
       </c>
       <c r="C5">
-        <v>7.629654219477611</v>
+        <v>30.68844264259262</v>
       </c>
       <c r="D5">
-        <v>0.09260327465062979</v>
+        <v>0.1706084965332423</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Estreita</t>
+          <t>Moderada</t>
         </is>
       </c>
     </row>
@@ -506,23 +506,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vulnerabilidade Jurídica</t>
+          <t>Organizacao Social</t>
         </is>
       </c>
       <c r="C6">
-        <v>30.68844264259262</v>
+        <v>8.40253021833796</v>
       </c>
       <c r="D6">
-        <v>0.1706084965332423</v>
+        <v>0.101150822222562</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Baixa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estreita</t>
         </is>
       </c>
     </row>
@@ -534,14 +534,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Organização Social</t>
+          <t>Vitalidade Linguistica</t>
         </is>
       </c>
       <c r="C7">
-        <v>8.40253021833796</v>
+        <v>4.849856232471125E-08</v>
       </c>
       <c r="D7">
-        <v>0.101150822222562</v>
+        <v>2.991635273407584E-09</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -549,6 +549,62 @@
         </is>
       </c>
       <c r="F7" t="inlineStr">
+        <is>
+          <t>Estreita</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Integracao ao Mercado</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>3.484765520565583E-08</v>
+      </c>
+      <c r="D8">
+        <v>2.050008407799427E-09</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Estreita</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Exposicao Climatica</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>9.09172822407833E-09</v>
+      </c>
+      <c r="D9">
+        <v>4.655057934973063E-10</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>Estreita</t>
         </is>
